--- a/data-raw/workbooks/kelpbio-1-full-nereo.xlsx
+++ b/data-raw/workbooks/kelpbio-1-full-nereo.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1484" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1490" uniqueCount="25">
   <si>
     <t>site</t>
   </si>
@@ -84,13 +84,16 @@
     <t>carbon_mass_ug</t>
   </si>
   <si>
-    <t>canopy_m2</t>
+    <t>tide_height_m</t>
   </si>
   <si>
-    <t>polygon_m2</t>
+    <t>plot_canopy_area_m2</t>
   </si>
   <si>
-    <t>tide_height_m</t>
+    <t>plot_boundary_area_m2</t>
+  </si>
+  <si>
+    <t>site_canopy_area_m2</t>
   </si>
 </sst>
 </file>
@@ -19241,10 +19244,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E94"/>
+  <dimension ref="A1:F99"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1">
+    <row r="1" spans="1:6" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -19260,8 +19263,11 @@
       <c r="E1" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -19269,16 +19275,16 @@
         <v>2020</v>
       </c>
       <c r="C2">
-        <v>40.16</v>
+        <v>1.07</v>
       </c>
       <c r="D2">
-        <v>251</v>
+        <v>36.06</v>
       </c>
       <c r="E2">
-        <v>1.39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>225.4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -19286,16 +19292,16 @@
         <v>2020</v>
       </c>
       <c r="C3">
-        <v>63.43</v>
+        <v>1.07</v>
       </c>
       <c r="D3">
-        <v>204.6</v>
+        <v>57.41</v>
       </c>
       <c r="E3">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>185.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -19303,16 +19309,16 @@
         <v>2020</v>
       </c>
       <c r="C4">
-        <v>186.15</v>
+        <v>1.07</v>
       </c>
       <c r="D4">
-        <v>219</v>
+        <v>217.51</v>
       </c>
       <c r="E4">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>255.9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -19320,16 +19326,19 @@
         <v>2020</v>
       </c>
       <c r="C5">
-        <v>117.24</v>
+        <v>0.37</v>
       </c>
       <c r="D5">
-        <v>189.1</v>
+        <v>116.81</v>
       </c>
       <c r="E5">
-        <v>0.91</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>188.4</v>
+      </c>
+      <c r="F5">
+        <v>9020</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -19337,16 +19346,19 @@
         <v>2020</v>
       </c>
       <c r="C6">
-        <v>121.53</v>
+        <v>0.37</v>
       </c>
       <c r="D6">
-        <v>276.2</v>
+        <v>105.78</v>
       </c>
       <c r="E6">
-        <v>1.21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>240.4</v>
+      </c>
+      <c r="F6">
+        <v>9020</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -19354,16 +19366,19 @@
         <v>2020</v>
       </c>
       <c r="C7">
-        <v>88.73999999999999</v>
+        <v>0.37</v>
       </c>
       <c r="D7">
-        <v>181.1</v>
+        <v>99.47</v>
       </c>
       <c r="E7">
-        <v>1.38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>203</v>
+      </c>
+      <c r="F7">
+        <v>9020</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -19371,16 +19386,19 @@
         <v>2020</v>
       </c>
       <c r="C8">
-        <v>42.73</v>
+        <v>0.58</v>
       </c>
       <c r="D8">
-        <v>237.4</v>
+        <v>49.81</v>
       </c>
       <c r="E8">
-        <v>1.27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>276.7</v>
+      </c>
+      <c r="F8">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -19388,16 +19406,19 @@
         <v>2020</v>
       </c>
       <c r="C9">
-        <v>230.76</v>
+        <v>0.58</v>
       </c>
       <c r="D9">
-        <v>256.4</v>
+        <v>216.45</v>
       </c>
       <c r="E9">
-        <v>0.91</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>240.5</v>
+      </c>
+      <c r="F9">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -19405,16 +19426,19 @@
         <v>2020</v>
       </c>
       <c r="C10">
-        <v>128.3</v>
+        <v>0.58</v>
       </c>
       <c r="D10">
-        <v>267.3</v>
+        <v>117.12</v>
       </c>
       <c r="E10">
-        <v>0.91</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>244</v>
+      </c>
+      <c r="F10">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -19422,16 +19446,19 @@
         <v>2020</v>
       </c>
       <c r="C11">
-        <v>163.85</v>
+        <v>0.14</v>
       </c>
       <c r="D11">
-        <v>184.1</v>
+        <v>241.99</v>
       </c>
       <c r="E11">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>271.9</v>
+      </c>
+      <c r="F11">
+        <v>8190</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -19439,16 +19466,19 @@
         <v>2020</v>
       </c>
       <c r="C12">
-        <v>204.26</v>
+        <v>0.14</v>
       </c>
       <c r="D12">
-        <v>246.1</v>
+        <v>161.68</v>
       </c>
       <c r="E12">
-        <v>0.93</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>194.8</v>
+      </c>
+      <c r="F12">
+        <v>8190</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -19456,16 +19486,19 @@
         <v>2020</v>
       </c>
       <c r="C13">
-        <v>171.39</v>
+        <v>0.14</v>
       </c>
       <c r="D13">
-        <v>267.8</v>
+        <v>136.26</v>
       </c>
       <c r="E13">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>212.9</v>
+      </c>
+      <c r="F13">
+        <v>8190</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -19473,16 +19506,19 @@
         <v>2020</v>
       </c>
       <c r="C14">
-        <v>242.19</v>
+        <v>1.44</v>
       </c>
       <c r="D14">
-        <v>269.1</v>
+        <v>227.88</v>
       </c>
       <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>253.2</v>
+      </c>
+      <c r="F14">
+        <v>6740</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -19490,16 +19526,19 @@
         <v>2020</v>
       </c>
       <c r="C15">
-        <v>149.06</v>
+        <v>1.44</v>
       </c>
       <c r="D15">
-        <v>236.6</v>
+        <v>156.3</v>
       </c>
       <c r="E15">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>248.1</v>
+      </c>
+      <c r="F15">
+        <v>6740</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>10</v>
       </c>
@@ -19507,16 +19546,19 @@
         <v>2020</v>
       </c>
       <c r="C16">
-        <v>98.15000000000001</v>
+        <v>1.44</v>
       </c>
       <c r="D16">
-        <v>239.4</v>
+        <v>96.72</v>
       </c>
       <c r="E16">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>235.9</v>
+      </c>
+      <c r="F16">
+        <v>6740</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>11</v>
       </c>
@@ -19524,16 +19566,19 @@
         <v>2020</v>
       </c>
       <c r="C17">
-        <v>90.93000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="D17">
-        <v>216.5</v>
+        <v>92.31999999999999</v>
       </c>
       <c r="E17">
-        <v>0.89</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>219.8</v>
+      </c>
+      <c r="F17">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>11</v>
       </c>
@@ -19541,16 +19586,19 @@
         <v>2020</v>
       </c>
       <c r="C18">
-        <v>99.22</v>
+        <v>0.02</v>
       </c>
       <c r="D18">
-        <v>215.7</v>
+        <v>86.11</v>
       </c>
       <c r="E18">
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>187.2</v>
+      </c>
+      <c r="F18">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -19558,16 +19606,19 @@
         <v>2020</v>
       </c>
       <c r="C19">
-        <v>179.32</v>
+        <v>0.02</v>
       </c>
       <c r="D19">
-        <v>239.1</v>
+        <v>209.85</v>
       </c>
       <c r="E19">
-        <v>0.57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>279.8</v>
+      </c>
+      <c r="F19">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -19575,16 +19626,19 @@
         <v>2021</v>
       </c>
       <c r="C20">
-        <v>47.97</v>
+        <v>0.86</v>
       </c>
       <c r="D20">
-        <v>266.5</v>
+        <v>32.78</v>
       </c>
       <c r="E20">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>182.1</v>
+      </c>
+      <c r="F20">
+        <v>7470</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -19592,16 +19646,19 @@
         <v>2021</v>
       </c>
       <c r="C21">
-        <v>181.11</v>
+        <v>0.86</v>
       </c>
       <c r="D21">
-        <v>248.1</v>
+        <v>164.54</v>
       </c>
       <c r="E21">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>225.4</v>
+      </c>
+      <c r="F21">
+        <v>7470</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -19609,16 +19666,19 @@
         <v>2021</v>
       </c>
       <c r="C22">
-        <v>129.78</v>
+        <v>0.86</v>
       </c>
       <c r="D22">
-        <v>193.7</v>
+        <v>130.32</v>
       </c>
       <c r="E22">
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>194.5</v>
+      </c>
+      <c r="F22">
+        <v>7470</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -19626,16 +19686,16 @@
         <v>2021</v>
       </c>
       <c r="C23">
-        <v>65.72</v>
+        <v>1.15</v>
       </c>
       <c r="D23">
-        <v>234.7</v>
+        <v>59.95</v>
       </c>
       <c r="E23">
-        <v>1.19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>214.1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
         <v>7</v>
       </c>
@@ -19643,16 +19703,16 @@
         <v>2021</v>
       </c>
       <c r="C24">
-        <v>86.73</v>
+        <v>1.15</v>
       </c>
       <c r="D24">
-        <v>247.8</v>
+        <v>71.16</v>
       </c>
       <c r="E24">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>203.3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
         <v>7</v>
       </c>
@@ -19660,16 +19720,16 @@
         <v>2021</v>
       </c>
       <c r="C25">
-        <v>128.04</v>
+        <v>1.15</v>
       </c>
       <c r="D25">
-        <v>232.8</v>
+        <v>104.33</v>
       </c>
       <c r="E25">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>189.7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
         <v>8</v>
       </c>
@@ -19677,16 +19737,19 @@
         <v>2021</v>
       </c>
       <c r="C26">
-        <v>126.43</v>
+        <v>1.31</v>
       </c>
       <c r="D26">
-        <v>188.7</v>
+        <v>153.9</v>
       </c>
       <c r="E26">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>229.7</v>
+      </c>
+      <c r="F26">
+        <v>6860</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
         <v>8</v>
       </c>
@@ -19694,16 +19757,19 @@
         <v>2021</v>
       </c>
       <c r="C27">
-        <v>220.22</v>
+        <v>1.31</v>
       </c>
       <c r="D27">
-        <v>242</v>
+        <v>215.94</v>
       </c>
       <c r="E27">
-        <v>1.14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+        <v>237.3</v>
+      </c>
+      <c r="F27">
+        <v>6860</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
         <v>8</v>
       </c>
@@ -19711,33 +19777,33 @@
         <v>2021</v>
       </c>
       <c r="C28">
-        <v>133.74</v>
+        <v>1.31</v>
       </c>
       <c r="D28">
-        <v>183.2</v>
+        <v>189.95</v>
       </c>
       <c r="E28">
-        <v>1.39</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+        <v>260.2</v>
+      </c>
+      <c r="F28">
+        <v>6860</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B29">
         <v>2021</v>
       </c>
       <c r="C29">
-        <v>133.4</v>
-      </c>
-      <c r="D29">
-        <v>226.1</v>
-      </c>
-      <c r="E29">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+        <v>0.06</v>
+      </c>
+      <c r="F29">
+        <v>7230</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
         <v>10</v>
       </c>
@@ -19745,16 +19811,19 @@
         <v>2021</v>
       </c>
       <c r="C30">
-        <v>170.4</v>
+        <v>0.99</v>
       </c>
       <c r="D30">
-        <v>213</v>
+        <v>126.91</v>
       </c>
       <c r="E30">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+        <v>215.1</v>
+      </c>
+      <c r="F30">
+        <v>5320</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31" t="s">
         <v>10</v>
       </c>
@@ -19762,50 +19831,53 @@
         <v>2021</v>
       </c>
       <c r="C31">
-        <v>73.02</v>
+        <v>0.99</v>
       </c>
       <c r="D31">
-        <v>243.4</v>
+        <v>180.24</v>
       </c>
       <c r="E31">
-        <v>0.93</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+        <v>225.3</v>
+      </c>
+      <c r="F31">
+        <v>5320</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B32">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C32">
-        <v>80.03</v>
+        <v>0.99</v>
       </c>
       <c r="D32">
-        <v>222.3</v>
+        <v>62.97</v>
       </c>
       <c r="E32">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
+        <v>209.9</v>
+      </c>
+      <c r="F32">
+        <v>5320</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B33">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C33">
-        <v>174.2</v>
-      </c>
-      <c r="D33">
-        <v>220.5</v>
-      </c>
-      <c r="E33">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+        <v>1.32</v>
+      </c>
+      <c r="F33">
+        <v>7340</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -19813,50 +19885,59 @@
         <v>2022</v>
       </c>
       <c r="C34">
-        <v>184.89</v>
+        <v>1.34</v>
       </c>
       <c r="D34">
-        <v>271.9</v>
+        <v>78.91</v>
       </c>
       <c r="E34">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
+        <v>219.2</v>
+      </c>
+      <c r="F34">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B35">
         <v>2022</v>
       </c>
       <c r="C35">
-        <v>88.70999999999999</v>
+        <v>1.34</v>
       </c>
       <c r="D35">
-        <v>260.9</v>
+        <v>176.17</v>
       </c>
       <c r="E35">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
+        <v>223</v>
+      </c>
+      <c r="F35">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B36">
         <v>2022</v>
       </c>
       <c r="C36">
-        <v>42.12</v>
+        <v>1.34</v>
       </c>
       <c r="D36">
-        <v>234</v>
+        <v>140.9</v>
       </c>
       <c r="E36">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
+        <v>207.2</v>
+      </c>
+      <c r="F36">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37" t="s">
         <v>7</v>
       </c>
@@ -19864,50 +19945,59 @@
         <v>2022</v>
       </c>
       <c r="C37">
-        <v>49.58</v>
+        <v>0.85</v>
       </c>
       <c r="D37">
-        <v>190.7</v>
+        <v>71.23</v>
       </c>
       <c r="E37">
-        <v>1.27</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
+        <v>209.5</v>
+      </c>
+      <c r="F37">
+        <v>3770</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B38">
         <v>2022</v>
       </c>
       <c r="C38">
-        <v>72.13</v>
+        <v>0.85</v>
       </c>
       <c r="D38">
-        <v>225.4</v>
+        <v>39.06</v>
       </c>
       <c r="E38">
-        <v>1.44</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
+        <v>217</v>
+      </c>
+      <c r="F38">
+        <v>3770</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B39">
         <v>2022</v>
       </c>
       <c r="C39">
-        <v>96.3</v>
+        <v>0.85</v>
       </c>
       <c r="D39">
-        <v>185.2</v>
+        <v>50.99</v>
       </c>
       <c r="E39">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
+        <v>196.1</v>
+      </c>
+      <c r="F39">
+        <v>3770</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40" t="s">
         <v>8</v>
       </c>
@@ -19915,50 +20005,59 @@
         <v>2022</v>
       </c>
       <c r="C40">
-        <v>76.77</v>
+        <v>0.89</v>
       </c>
       <c r="D40">
-        <v>255.9</v>
+        <v>70.56</v>
       </c>
       <c r="E40">
-        <v>1.29</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
+        <v>220.5</v>
+      </c>
+      <c r="F40">
+        <v>5360</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B41">
         <v>2022</v>
       </c>
       <c r="C41">
-        <v>131.88</v>
+        <v>0.89</v>
       </c>
       <c r="D41">
-        <v>188.4</v>
+        <v>142.22</v>
       </c>
       <c r="E41">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
+        <v>273.5</v>
+      </c>
+      <c r="F41">
+        <v>5360</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B42">
         <v>2022</v>
       </c>
       <c r="C42">
-        <v>38.46</v>
+        <v>0.89</v>
       </c>
       <c r="D42">
-        <v>240.4</v>
+        <v>59.82</v>
       </c>
       <c r="E42">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
+        <v>199.4</v>
+      </c>
+      <c r="F42">
+        <v>5360</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
       <c r="A43" t="s">
         <v>9</v>
       </c>
@@ -19966,880 +20065,1118 @@
         <v>2022</v>
       </c>
       <c r="C43">
-        <v>89.31999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="D43">
-        <v>203</v>
+        <v>158.48</v>
       </c>
       <c r="E43">
-        <v>1.31</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
+        <v>226.4</v>
+      </c>
+      <c r="F43">
+        <v>9040</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B44">
         <v>2022</v>
       </c>
       <c r="C44">
-        <v>152.18</v>
+        <v>0.55</v>
       </c>
       <c r="D44">
-        <v>276.7</v>
+        <v>31.98</v>
       </c>
       <c r="E44">
-        <v>1.41</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
+        <v>199.9</v>
+      </c>
+      <c r="F44">
+        <v>9040</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B45">
         <v>2022</v>
       </c>
       <c r="C45">
-        <v>36.08</v>
+        <v>0.55</v>
       </c>
       <c r="D45">
-        <v>240.5</v>
+        <v>107.8</v>
       </c>
       <c r="E45">
-        <v>1.31</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
+        <v>245</v>
+      </c>
+      <c r="F45">
+        <v>9040</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B46">
         <v>2022</v>
       </c>
       <c r="C46">
-        <v>146.4</v>
-      </c>
-      <c r="D46">
-        <v>244</v>
-      </c>
-      <c r="E46">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
+        <v>0.54</v>
+      </c>
+      <c r="F46">
+        <v>9330</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
       <c r="A47" t="s">
+        <v>11</v>
+      </c>
+      <c r="B47">
+        <v>2022</v>
+      </c>
+      <c r="C47">
+        <v>0.89</v>
+      </c>
+      <c r="D47">
+        <v>123.75</v>
+      </c>
+      <c r="E47">
+        <v>225</v>
+      </c>
+      <c r="F47">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" t="s">
+        <v>11</v>
+      </c>
+      <c r="B48">
+        <v>2022</v>
+      </c>
+      <c r="C48">
+        <v>0.89</v>
+      </c>
+      <c r="D48">
+        <v>41.16</v>
+      </c>
+      <c r="E48">
+        <v>274.4</v>
+      </c>
+      <c r="F48">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" t="s">
+        <v>11</v>
+      </c>
+      <c r="B49">
+        <v>2022</v>
+      </c>
+      <c r="C49">
+        <v>0.89</v>
+      </c>
+      <c r="D49">
+        <v>133.44</v>
+      </c>
+      <c r="E49">
+        <v>222.4</v>
+      </c>
+      <c r="F49">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" t="s">
         <v>6</v>
       </c>
-      <c r="B47">
-        <v>2023</v>
-      </c>
-      <c r="C47">
-        <v>73.41</v>
-      </c>
-      <c r="D47">
-        <v>271.9</v>
-      </c>
-      <c r="E47">
-        <v>0.61</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" t="s">
+      <c r="B50">
+        <v>2023</v>
+      </c>
+      <c r="C50">
+        <v>1.3</v>
+      </c>
+      <c r="D50">
+        <v>67.88</v>
+      </c>
+      <c r="E50">
+        <v>251.4</v>
+      </c>
+      <c r="F50">
+        <v>5460</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" t="s">
         <v>6</v>
       </c>
-      <c r="B48">
-        <v>2023</v>
-      </c>
-      <c r="C48">
-        <v>83.76000000000001</v>
-      </c>
-      <c r="D48">
-        <v>194.8</v>
-      </c>
-      <c r="E48">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" t="s">
+      <c r="B51">
+        <v>2023</v>
+      </c>
+      <c r="C51">
+        <v>1.3</v>
+      </c>
+      <c r="D51">
+        <v>102.81</v>
+      </c>
+      <c r="E51">
+        <v>239.1</v>
+      </c>
+      <c r="F51">
+        <v>5460</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" t="s">
         <v>6</v>
       </c>
-      <c r="B49">
-        <v>2023</v>
-      </c>
-      <c r="C49">
-        <v>138.38</v>
-      </c>
-      <c r="D49">
-        <v>212.9</v>
-      </c>
-      <c r="E49">
+      <c r="B52">
+        <v>2023</v>
+      </c>
+      <c r="C52">
+        <v>1.3</v>
+      </c>
+      <c r="D52">
+        <v>178.56</v>
+      </c>
+      <c r="E52">
+        <v>274.7</v>
+      </c>
+      <c r="F52">
+        <v>5460</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" t="s">
+        <v>7</v>
+      </c>
+      <c r="B53">
+        <v>2023</v>
+      </c>
+      <c r="C53">
+        <v>1.02</v>
+      </c>
+      <c r="D53">
+        <v>165.98</v>
+      </c>
+      <c r="E53">
+        <v>221.3</v>
+      </c>
+      <c r="F53">
+        <v>6110</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" t="s">
+        <v>7</v>
+      </c>
+      <c r="B54">
+        <v>2023</v>
+      </c>
+      <c r="C54">
+        <v>1.02</v>
+      </c>
+      <c r="D54">
+        <v>122.96</v>
+      </c>
+      <c r="E54">
+        <v>212</v>
+      </c>
+      <c r="F54">
+        <v>6110</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" t="s">
+        <v>7</v>
+      </c>
+      <c r="B55">
+        <v>2023</v>
+      </c>
+      <c r="C55">
+        <v>1.02</v>
+      </c>
+      <c r="D55">
+        <v>92.37</v>
+      </c>
+      <c r="E55">
+        <v>279.9</v>
+      </c>
+      <c r="F55">
+        <v>6110</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" t="s">
+        <v>8</v>
+      </c>
+      <c r="B56">
+        <v>2023</v>
+      </c>
+      <c r="C56">
         <v>0.21</v>
       </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" t="s">
-        <v>7</v>
-      </c>
-      <c r="B50">
-        <v>2023</v>
-      </c>
-      <c r="C50">
-        <v>189.9</v>
-      </c>
-      <c r="D50">
-        <v>253.2</v>
-      </c>
-      <c r="E50">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" t="s">
-        <v>7</v>
-      </c>
-      <c r="B51">
-        <v>2023</v>
-      </c>
-      <c r="C51">
-        <v>143.9</v>
-      </c>
-      <c r="D51">
-        <v>248.1</v>
-      </c>
-      <c r="E51">
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" t="s">
-        <v>7</v>
-      </c>
-      <c r="B52">
-        <v>2023</v>
-      </c>
-      <c r="C52">
-        <v>77.84999999999999</v>
-      </c>
-      <c r="D52">
-        <v>235.9</v>
-      </c>
-      <c r="E52">
-        <v>1.07</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" t="s">
+      <c r="D56">
+        <v>44.75</v>
+      </c>
+      <c r="E56">
+        <v>203.4</v>
+      </c>
+      <c r="F56">
+        <v>8760</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" t="s">
         <v>8</v>
       </c>
-      <c r="B53">
-        <v>2023</v>
-      </c>
-      <c r="C53">
-        <v>48.36</v>
-      </c>
-      <c r="D53">
-        <v>219.8</v>
-      </c>
-      <c r="E53">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" t="s">
+      <c r="B57">
+        <v>2023</v>
+      </c>
+      <c r="C57">
+        <v>0.21</v>
+      </c>
+      <c r="D57">
+        <v>60.21</v>
+      </c>
+      <c r="E57">
+        <v>273.7</v>
+      </c>
+      <c r="F57">
+        <v>8760</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" t="s">
         <v>8</v>
       </c>
-      <c r="B54">
-        <v>2023</v>
-      </c>
-      <c r="C54">
-        <v>41.18</v>
-      </c>
-      <c r="D54">
-        <v>187.2</v>
-      </c>
-      <c r="E54">
-        <v>1.33</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" t="s">
-        <v>8</v>
-      </c>
-      <c r="B55">
-        <v>2023</v>
-      </c>
-      <c r="C55">
-        <v>109.12</v>
-      </c>
-      <c r="D55">
-        <v>279.8</v>
-      </c>
-      <c r="E55">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" t="s">
-        <v>9</v>
-      </c>
-      <c r="B56">
-        <v>2023</v>
-      </c>
-      <c r="C56">
-        <v>120.19</v>
-      </c>
-      <c r="D56">
-        <v>182.1</v>
-      </c>
-      <c r="E56">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" t="s">
-        <v>9</v>
-      </c>
-      <c r="B57">
-        <v>2023</v>
-      </c>
-      <c r="C57">
-        <v>33.81</v>
-      </c>
-      <c r="D57">
-        <v>225.4</v>
-      </c>
-      <c r="E57">
-        <v>0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" t="s">
-        <v>9</v>
-      </c>
       <c r="B58">
         <v>2023</v>
       </c>
       <c r="C58">
-        <v>60.3</v>
+        <v>0.21</v>
       </c>
       <c r="D58">
-        <v>194.5</v>
+        <v>76.17</v>
       </c>
       <c r="E58">
+        <v>195.3</v>
+      </c>
+      <c r="F58">
+        <v>8760</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" t="s">
+        <v>9</v>
+      </c>
+      <c r="B59">
+        <v>2023</v>
+      </c>
+      <c r="C59">
+        <v>0.82</v>
+      </c>
+      <c r="D59">
+        <v>180.05</v>
+      </c>
+      <c r="E59">
+        <v>272.8</v>
+      </c>
+      <c r="F59">
+        <v>2870</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" t="s">
+        <v>9</v>
+      </c>
+      <c r="B60">
+        <v>2023</v>
+      </c>
+      <c r="C60">
+        <v>0.82</v>
+      </c>
+      <c r="D60">
+        <v>27.39</v>
+      </c>
+      <c r="E60">
+        <v>182.6</v>
+      </c>
+      <c r="F60">
+        <v>2870</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" t="s">
+        <v>9</v>
+      </c>
+      <c r="B61">
+        <v>2023</v>
+      </c>
+      <c r="C61">
+        <v>0.82</v>
+      </c>
+      <c r="D61">
+        <v>65.78</v>
+      </c>
+      <c r="E61">
+        <v>212.2</v>
+      </c>
+      <c r="F61">
+        <v>2870</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" t="s">
+        <v>10</v>
+      </c>
+      <c r="B62">
+        <v>2023</v>
+      </c>
+      <c r="C62">
         <v>1.02</v>
       </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" t="s">
+      <c r="D62">
+        <v>209.58</v>
+      </c>
+      <c r="E62">
+        <v>240.9</v>
+      </c>
+      <c r="F62">
+        <v>9410</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" t="s">
         <v>10</v>
       </c>
-      <c r="B59">
-        <v>2023</v>
-      </c>
-      <c r="C59">
-        <v>186.27</v>
-      </c>
-      <c r="D59">
-        <v>214.1</v>
-      </c>
-      <c r="E59">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" t="s">
+      <c r="B63">
+        <v>2023</v>
+      </c>
+      <c r="C63">
+        <v>1.02</v>
+      </c>
+      <c r="D63">
+        <v>224.37</v>
+      </c>
+      <c r="E63">
+        <v>260.9</v>
+      </c>
+      <c r="F63">
+        <v>9410</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" t="s">
         <v>10</v>
       </c>
-      <c r="B60">
-        <v>2023</v>
-      </c>
-      <c r="C60">
-        <v>174.84</v>
-      </c>
-      <c r="D60">
-        <v>203.3</v>
-      </c>
-      <c r="E60">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" t="s">
-        <v>10</v>
-      </c>
-      <c r="B61">
-        <v>2023</v>
-      </c>
-      <c r="C61">
-        <v>136.58</v>
-      </c>
-      <c r="D61">
-        <v>189.7</v>
-      </c>
-      <c r="E61">
-        <v>1.44</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" t="s">
+      <c r="B64">
+        <v>2023</v>
+      </c>
+      <c r="C64">
+        <v>1.02</v>
+      </c>
+      <c r="D64">
+        <v>195.84</v>
+      </c>
+      <c r="E64">
+        <v>272</v>
+      </c>
+      <c r="F64">
+        <v>9410</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65" t="s">
         <v>11</v>
       </c>
-      <c r="B62">
-        <v>2023</v>
-      </c>
-      <c r="C62">
-        <v>94.18000000000001</v>
-      </c>
-      <c r="D62">
-        <v>229.7</v>
-      </c>
-      <c r="E62">
-        <v>0.89</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" t="s">
+      <c r="B65">
+        <v>2023</v>
+      </c>
+      <c r="C65">
+        <v>0.79</v>
+      </c>
+      <c r="D65">
+        <v>108.49</v>
+      </c>
+      <c r="E65">
+        <v>264.6</v>
+      </c>
+      <c r="F65">
+        <v>9090</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" t="s">
         <v>11</v>
       </c>
-      <c r="B63">
-        <v>2023</v>
-      </c>
-      <c r="C63">
-        <v>130.51</v>
-      </c>
-      <c r="D63">
-        <v>237.3</v>
-      </c>
-      <c r="E63">
-        <v>0.52</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" t="s">
+      <c r="B66">
+        <v>2023</v>
+      </c>
+      <c r="C66">
+        <v>0.79</v>
+      </c>
+      <c r="D66">
+        <v>132.44</v>
+      </c>
+      <c r="E66">
+        <v>240.8</v>
+      </c>
+      <c r="F66">
+        <v>9090</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" t="s">
         <v>11</v>
       </c>
-      <c r="B64">
-        <v>2023</v>
-      </c>
-      <c r="C64">
-        <v>187.34</v>
-      </c>
-      <c r="D64">
-        <v>260.2</v>
-      </c>
-      <c r="E64">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" t="s">
+      <c r="B67">
+        <v>2023</v>
+      </c>
+      <c r="C67">
+        <v>0.79</v>
+      </c>
+      <c r="D67">
+        <v>173.09</v>
+      </c>
+      <c r="E67">
+        <v>240.4</v>
+      </c>
+      <c r="F67">
+        <v>9090</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68" t="s">
         <v>6</v>
-      </c>
-      <c r="B65">
-        <v>2024</v>
-      </c>
-      <c r="C65">
-        <v>152.9</v>
-      </c>
-      <c r="D65">
-        <v>242.7</v>
-      </c>
-      <c r="E65">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" t="s">
-        <v>6</v>
-      </c>
-      <c r="B66">
-        <v>2024</v>
-      </c>
-      <c r="C66">
-        <v>135.51</v>
-      </c>
-      <c r="D66">
-        <v>215.1</v>
-      </c>
-      <c r="E66">
-        <v>1.08</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" t="s">
-        <v>6</v>
-      </c>
-      <c r="B67">
-        <v>2024</v>
-      </c>
-      <c r="C67">
-        <v>72.09999999999999</v>
-      </c>
-      <c r="D67">
-        <v>225.3</v>
-      </c>
-      <c r="E67">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" t="s">
-        <v>8</v>
       </c>
       <c r="B68">
         <v>2024</v>
       </c>
       <c r="C68">
-        <v>67.17</v>
+        <v>0.13</v>
       </c>
       <c r="D68">
-        <v>209.9</v>
+        <v>162.22</v>
       </c>
       <c r="E68">
-        <v>1.32</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
+        <v>257.5</v>
+      </c>
+      <c r="F68">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B69">
         <v>2024</v>
       </c>
       <c r="C69">
-        <v>84.83</v>
+        <v>0.13</v>
       </c>
       <c r="D69">
-        <v>188.5</v>
+        <v>152.59</v>
       </c>
       <c r="E69">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
+        <v>242.2</v>
+      </c>
+      <c r="F69">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B70">
         <v>2024</v>
       </c>
       <c r="C70">
-        <v>192.9</v>
+        <v>0.13</v>
       </c>
       <c r="D70">
-        <v>219.2</v>
+        <v>69.25</v>
       </c>
       <c r="E70">
-        <v>1.28</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
+        <v>216.4</v>
+      </c>
+      <c r="F70">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B71">
         <v>2024</v>
       </c>
       <c r="C71">
-        <v>198.47</v>
-      </c>
-      <c r="D71">
-        <v>223</v>
-      </c>
-      <c r="E71">
         <v>0.93</v>
       </c>
-    </row>
-    <row r="72" spans="1:5">
+      <c r="F71">
+        <v>5760</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
       <c r="A72" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B72">
         <v>2024</v>
       </c>
       <c r="C72">
-        <v>149.18</v>
+        <v>0.05</v>
       </c>
       <c r="D72">
-        <v>207.2</v>
+        <v>66.94</v>
       </c>
       <c r="E72">
-        <v>1.22</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
+        <v>209.2</v>
+      </c>
+      <c r="F72">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B73">
         <v>2024</v>
       </c>
       <c r="C73">
-        <v>148.74</v>
+        <v>0.05</v>
       </c>
       <c r="D73">
-        <v>209.5</v>
+        <v>86.72</v>
       </c>
       <c r="E73">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
+        <v>192.7</v>
+      </c>
+      <c r="F73">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B74">
         <v>2024</v>
       </c>
       <c r="C74">
-        <v>121.52</v>
+        <v>0.05</v>
       </c>
       <c r="D74">
-        <v>217</v>
+        <v>210.58</v>
       </c>
       <c r="E74">
-        <v>1.17</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
+        <v>239.3</v>
+      </c>
+      <c r="F74">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B75">
         <v>2024</v>
       </c>
       <c r="C75">
-        <v>29.41</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D75">
-        <v>196.1</v>
+        <v>222.5</v>
       </c>
       <c r="E75">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
+        <v>250</v>
+      </c>
+      <c r="F75">
+        <v>8770</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B76">
         <v>2024</v>
       </c>
       <c r="C76">
-        <v>136.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D76">
-        <v>220.5</v>
+        <v>157.18</v>
       </c>
       <c r="E76">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
+        <v>218.3</v>
+      </c>
+      <c r="F76">
+        <v>8770</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B77">
         <v>2024</v>
       </c>
       <c r="C77">
-        <v>216.06</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D77">
-        <v>273.5</v>
+        <v>134.4</v>
       </c>
       <c r="E77">
-        <v>1.38</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
+        <v>189.3</v>
+      </c>
+      <c r="F77">
+        <v>8770</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B78">
         <v>2024</v>
       </c>
       <c r="C78">
-        <v>145.56</v>
+        <v>0.5</v>
       </c>
       <c r="D78">
-        <v>199.4</v>
+        <v>112</v>
       </c>
       <c r="E78">
-        <v>1.39</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
+        <v>200</v>
+      </c>
+      <c r="F78">
+        <v>5240</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B79">
         <v>2024</v>
       </c>
       <c r="C79">
-        <v>113.2</v>
+        <v>0.5</v>
       </c>
       <c r="D79">
-        <v>226.4</v>
+        <v>34.05</v>
       </c>
       <c r="E79">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
+        <v>227</v>
+      </c>
+      <c r="F79">
+        <v>5240</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
       <c r="A80" t="s">
+        <v>10</v>
+      </c>
+      <c r="B80">
+        <v>2024</v>
+      </c>
+      <c r="C80">
+        <v>0.5</v>
+      </c>
+      <c r="D80">
+        <v>160.95</v>
+      </c>
+      <c r="E80">
+        <v>259.6</v>
+      </c>
+      <c r="F80">
+        <v>5240</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81" t="s">
+        <v>11</v>
+      </c>
+      <c r="B81">
+        <v>2024</v>
+      </c>
+      <c r="C81">
+        <v>0.95</v>
+      </c>
+      <c r="D81">
+        <v>156.97</v>
+      </c>
+      <c r="E81">
+        <v>198.7</v>
+      </c>
+      <c r="F81">
+        <v>8240</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82" t="s">
+        <v>11</v>
+      </c>
+      <c r="B82">
+        <v>2024</v>
+      </c>
+      <c r="C82">
+        <v>0.95</v>
+      </c>
+      <c r="D82">
+        <v>199.36</v>
+      </c>
+      <c r="E82">
+        <v>273.1</v>
+      </c>
+      <c r="F82">
+        <v>8240</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83" t="s">
+        <v>11</v>
+      </c>
+      <c r="B83">
+        <v>2024</v>
+      </c>
+      <c r="C83">
+        <v>0.95</v>
+      </c>
+      <c r="D83">
+        <v>112.7</v>
+      </c>
+      <c r="E83">
+        <v>225.4</v>
+      </c>
+      <c r="F83">
+        <v>8240</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84" t="s">
         <v>6</v>
-      </c>
-      <c r="B80">
-        <v>2025</v>
-      </c>
-      <c r="C80">
-        <v>111.94</v>
-      </c>
-      <c r="D80">
-        <v>199.9</v>
-      </c>
-      <c r="E80">
-        <v>0.89</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" t="s">
-        <v>6</v>
-      </c>
-      <c r="B81">
-        <v>2025</v>
-      </c>
-      <c r="C81">
-        <v>137.2</v>
-      </c>
-      <c r="D81">
-        <v>245</v>
-      </c>
-      <c r="E81">
-        <v>0.98</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" t="s">
-        <v>6</v>
-      </c>
-      <c r="B82">
-        <v>2025</v>
-      </c>
-      <c r="C82">
-        <v>35.1</v>
-      </c>
-      <c r="D82">
-        <v>234</v>
-      </c>
-      <c r="E82">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" t="s">
-        <v>7</v>
-      </c>
-      <c r="B83">
-        <v>2025</v>
-      </c>
-      <c r="C83">
-        <v>94.5</v>
-      </c>
-      <c r="D83">
-        <v>225</v>
-      </c>
-      <c r="E83">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" t="s">
-        <v>7</v>
       </c>
       <c r="B84">
         <v>2025</v>
       </c>
       <c r="C84">
-        <v>170.13</v>
+        <v>0.63</v>
       </c>
       <c r="D84">
-        <v>274.4</v>
+        <v>143.25</v>
       </c>
       <c r="E84">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
+        <v>255.8</v>
+      </c>
+      <c r="F84">
+        <v>7480</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B85">
         <v>2025</v>
       </c>
       <c r="C85">
-        <v>175.7</v>
+        <v>0.63</v>
       </c>
       <c r="D85">
-        <v>222.4</v>
+        <v>152.54</v>
       </c>
       <c r="E85">
-        <v>1.42</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
+        <v>272.4</v>
+      </c>
+      <c r="F85">
+        <v>7480</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
       <c r="A86" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B86">
         <v>2025</v>
       </c>
       <c r="C86">
-        <v>105.59</v>
+        <v>0.63</v>
       </c>
       <c r="D86">
-        <v>251.4</v>
+        <v>28.56</v>
       </c>
       <c r="E86">
-        <v>0.72</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
+        <v>190.4</v>
+      </c>
+      <c r="F86">
+        <v>7480</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B87">
         <v>2025</v>
       </c>
       <c r="C87">
-        <v>112.38</v>
+        <v>0.61</v>
       </c>
       <c r="D87">
-        <v>239.1</v>
+        <v>81.23</v>
       </c>
       <c r="E87">
-        <v>1.26</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5">
+        <v>193.4</v>
+      </c>
+      <c r="F87">
+        <v>8050</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B88">
         <v>2025</v>
       </c>
       <c r="C88">
-        <v>162.07</v>
+        <v>0.61</v>
       </c>
       <c r="D88">
-        <v>274.7</v>
+        <v>149.85</v>
       </c>
       <c r="E88">
-        <v>0.57</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5">
+        <v>241.7</v>
+      </c>
+      <c r="F88">
+        <v>8050</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B89">
         <v>2025</v>
       </c>
       <c r="C89">
-        <v>132.78</v>
+        <v>0.61</v>
       </c>
       <c r="D89">
-        <v>221.3</v>
+        <v>187.62</v>
       </c>
       <c r="E89">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
+        <v>237.5</v>
+      </c>
+      <c r="F89">
+        <v>8050</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
       <c r="A90" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B90">
         <v>2025</v>
       </c>
       <c r="C90">
-        <v>148.4</v>
-      </c>
-      <c r="D90">
-        <v>212</v>
-      </c>
-      <c r="E90">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5">
+        <v>1.38</v>
+      </c>
+      <c r="F90">
+        <v>4790</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B91">
         <v>2025</v>
       </c>
       <c r="C91">
-        <v>125.95</v>
+        <v>1.21</v>
       </c>
       <c r="D91">
-        <v>279.9</v>
+        <v>76.31</v>
       </c>
       <c r="E91">
-        <v>0.43</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5">
+        <v>181.7</v>
+      </c>
+      <c r="F91">
+        <v>7080</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B92">
         <v>2025</v>
       </c>
       <c r="C92">
-        <v>174.92</v>
+        <v>1.21</v>
       </c>
       <c r="D92">
-        <v>203.4</v>
+        <v>93.39</v>
       </c>
       <c r="E92">
-        <v>1.44</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5">
+        <v>198.7</v>
+      </c>
+      <c r="F92">
+        <v>7080</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B93">
         <v>2025</v>
       </c>
       <c r="C93">
-        <v>243.59</v>
+        <v>1.21</v>
       </c>
       <c r="D93">
-        <v>273.7</v>
+        <v>110.15</v>
       </c>
       <c r="E93">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5">
+        <v>186.7</v>
+      </c>
+      <c r="F93">
+        <v>7080</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B94">
         <v>2025</v>
       </c>
       <c r="C94">
-        <v>64.45</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D94">
-        <v>195.3</v>
+        <v>158.64</v>
       </c>
       <c r="E94">
-        <v>1.19</v>
+        <v>264.4</v>
+      </c>
+      <c r="F94">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95" t="s">
+        <v>10</v>
+      </c>
+      <c r="B95">
+        <v>2025</v>
+      </c>
+      <c r="C95">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="D95">
+        <v>192.99</v>
+      </c>
+      <c r="E95">
+        <v>275.7</v>
+      </c>
+      <c r="F95">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" t="s">
+        <v>10</v>
+      </c>
+      <c r="B96">
+        <v>2025</v>
+      </c>
+      <c r="C96">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="D96">
+        <v>89.06</v>
+      </c>
+      <c r="E96">
+        <v>197.9</v>
+      </c>
+      <c r="F96">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97" t="s">
+        <v>11</v>
+      </c>
+      <c r="B97">
+        <v>2025</v>
+      </c>
+      <c r="C97">
+        <v>0.16</v>
+      </c>
+      <c r="D97">
+        <v>228.93</v>
+      </c>
+      <c r="E97">
+        <v>266.2</v>
+      </c>
+      <c r="F97">
+        <v>8210</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98" t="s">
+        <v>11</v>
+      </c>
+      <c r="B98">
+        <v>2025</v>
+      </c>
+      <c r="C98">
+        <v>0.16</v>
+      </c>
+      <c r="D98">
+        <v>185.39</v>
+      </c>
+      <c r="E98">
+        <v>208.3</v>
+      </c>
+      <c r="F98">
+        <v>8210</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99" t="s">
+        <v>11</v>
+      </c>
+      <c r="B99">
+        <v>2025</v>
+      </c>
+      <c r="C99">
+        <v>0.16</v>
+      </c>
+      <c r="D99">
+        <v>65.14</v>
+      </c>
+      <c r="E99">
+        <v>197.4</v>
+      </c>
+      <c r="F99">
+        <v>8210</v>
       </c>
     </row>
   </sheetData>

--- a/data-raw/workbooks/kelpbio-1-full-nereo.xlsx
+++ b/data-raw/workbooks/kelpbio-1-full-nereo.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="weight" sheetId="1" r:id="rId1"/>
-    <sheet name="size" sheetId="2" r:id="rId2"/>
+    <sheet name="size_sample" sheetId="2" r:id="rId2"/>
     <sheet name="survey" sheetId="3" r:id="rId3"/>
     <sheet name="canopy" sheetId="4" r:id="rId4"/>
     <sheet name="wetdry" sheetId="5" r:id="rId5"/>
